--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:13</t>
+    <t xml:space="preserve">2026-09-09 21:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:19</t>
+    <t xml:space="preserve">2026-09-18 09:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:14</t>
+    <t xml:space="preserve">2026-09-25 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2023_los_rios.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:35</t>
+    <t xml:space="preserve">2026-10-05 02:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -588,7 +588,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>444219.12</v>
+        <v>444219.13</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>527499.62</v>
+        <v>527499.63</v>
       </c>
     </row>
     <row r="6">
